--- a/race_registration_forms/041_cycling_club_race_tournament_entry_form--race_registration_forms.xlsx
+++ b/race_registration_forms/041_cycling_club_race_tournament_entry_form--race_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -753,7 +753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -1257,34 +1257,34 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>race_day_select_one_choices</t>
+          <t>start_time_select_one_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>6:00-8:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>6:00-8:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>race_day_select_one_choices</t>
+          <t>start_time_select_one_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>8:00-10:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>8:00-10:00</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>6:00-8:00</t>
+          <t>10:00-12:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>6:00-8:00</t>
+          <t>10:00-12:00</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>8:00-10:00</t>
+          <t>12:00-14:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>8:00-10:00</t>
+          <t>12:00-14:00</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10:00-12:00</t>
+          <t>14:00-16:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>10:00-12:00</t>
+          <t>14:00-16:00</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12:00-14:00</t>
+          <t>16:00-18:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>12:00-14:00</t>
+          <t>16:00-18:00</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14:00-16:00</t>
+          <t>18:00-20:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>14:00-16:00</t>
+          <t>18:00-20:00</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16:00-18:00</t>
+          <t>20:00-22:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>16:00-18:00</t>
+          <t>20:00-22:00</t>
         </is>
       </c>
     </row>
@@ -1398,46 +1398,46 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>18:00-20:00</t>
+          <t>22:00-00:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>18:00-20:00</t>
+          <t>22:00-00:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>start_time_select_one_choices</t>
+          <t>finish_time_select_one_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20:00-22:00</t>
+          <t>8:00-10:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>20:00-22:00</t>
+          <t>8:00-10:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>start_time_select_one_choices</t>
+          <t>finish_time_select_one_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>22:00-00:00</t>
+          <t>10:00-12:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>22:00-00:00</t>
+          <t>10:00-12:00</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>8:00-10:00</t>
+          <t>12:00-14:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>8:00-10:00</t>
+          <t>12:00-14:00</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10:00-12:00</t>
+          <t>14:00-16:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>10:00-12:00</t>
+          <t>14:00-16:00</t>
         </is>
       </c>
     </row>
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>12:00-14:00</t>
+          <t>16:00-18:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>12:00-14:00</t>
+          <t>16:00-18:00</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14:00-16:00</t>
+          <t>18:00-20:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>14:00-16:00</t>
+          <t>18:00-20:00</t>
         </is>
       </c>
     </row>
@@ -1517,12 +1517,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:00-18:00</t>
+          <t>20:00-22:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>16:00-18:00</t>
+          <t>20:00-22:00</t>
         </is>
       </c>
     </row>
@@ -1534,44 +1534,10 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>18:00-20:00</t>
+          <t>22:00-00:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
-        <is>
-          <t>18:00-20:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>finish_time_select_one_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>20:00-22:00</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>20:00-22:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>finish_time_select_one_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>22:00-00:00</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
         <is>
           <t>22:00-00:00</t>
         </is>
